--- a/excel-data/restaurant_category.xlsx
+++ b/excel-data/restaurant_category.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6482D419-93AA-4754-BE8E-CEFEBA34B514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C98E37-3453-4754-8733-A26E0912C947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="1164" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurant_category" sheetId="1" r:id="rId1"/>
@@ -39,14 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>群組內排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>display_order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>資料建立時間</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,6 +79,14 @@
   </si>
   <si>
     <t>2026-05-02 16:32:16</t>
+  </si>
+  <si>
+    <t>display_order_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群組內排序 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -530,19 +530,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -553,13 +553,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -573,10 +573,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -590,10 +590,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -607,10 +607,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
